--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481164.0898654459</v>
+        <v>481164</v>
       </c>
       <c r="R2" t="n">
-        <v>6362025.585229632</v>
+        <v>6362026</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481164.0898654459</v>
+        <v>481164</v>
       </c>
       <c r="R3" t="n">
-        <v>6362025.585229632</v>
+        <v>6362026</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1980-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97520</v>
+        <v>97525</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97525</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17347-2025 artfynd.xlsx
+++ b/artfynd/A 17347-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74604492</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74601959</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
